--- a/tasks/finalpool/fetch-notion-monitoring/groundtruth_workspace/Service_Availability_Report.xlsx
+++ b/tasks/finalpool/fetch-notion-monitoring/groundtruth_workspace/Service_Availability_Report.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Service Status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Availability Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incidents" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,77 +425,243 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Total_Checks</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Up_Count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Down_Count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Degraded_Count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Uptime_Pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Last_Incident</t>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Avg_Response_Time_Ms</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Database Cluster</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
+          <t>API Gateway</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>168</v>
       </c>
       <c r="C2" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
+        <v>164</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>312.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>API Gateway</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
+          <t>Auth Service</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>168</v>
       </c>
       <c r="C3" t="n">
-        <v>99.95</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+        <v>166</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>87.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Storage Service</t>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>168</v>
+      </c>
+      <c r="C4" t="n">
+        <v>168</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35.08</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Service_Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Start_Time</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>End_Time</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration_Minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Error_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>API Gateway</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-03-01T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Connection timeout - upstream server not responding</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>API Gateway</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-04T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>502 Bad Gateway - backend service unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Auth Service</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
+          <t>2026-03-02T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>120</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>High latency detected on authentication requests</t>
         </is>
       </c>
     </row>
